--- a/output/pdf_financials_xlsx/LVG.xlsx
+++ b/output/pdf_financials_xlsx/LVG.xlsx
@@ -5886,37 +5886,37 @@
         <v>2.682239</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>6.898579</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>6.128347</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>5.796737</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>6.189767</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>5.985341</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>5.789435</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>5.73841</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>6.258421</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>6.101764</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>6.644963</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>6.293248</v>
       </c>
     </row>
     <row r="92">
@@ -5941,40 +5941,40 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>13.993948</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.116248</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.580002</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>15.617035</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.455171</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>16.465226</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>16.939113</v>
       </c>
     </row>
     <row r="93">
@@ -7430,10 +7430,10 @@
         <v>-0.8583730000000001</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.379182</v>
+        <v>-12.454804</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.020407</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>-3.288771</v>
@@ -10535,7 +10535,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10733,7 +10737,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11566,7 +11574,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -25156,7 +25168,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LVG.xlsx
+++ b/output/pdf_financials_xlsx/LVG.xlsx
@@ -1038,19 +1038,19 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.043391</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001852</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.007494</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000687</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1065,19 +1065,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.00215</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.005739</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.007698</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.011312</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.011046</v>
       </c>
     </row>
     <row r="13">
@@ -2046,19 +2046,19 @@
         <v>-1.530021</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-4.565272</v>
+        <v>-4.608663</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.423439</v>
+        <v>-2.425291</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.477288</v>
+        <v>-1.484782</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.690362</v>
+        <v>-0.691049</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-20.611176</v>
+        <v>-20.61129</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.543435</v>
@@ -2073,19 +2073,19 @@
         <v>-0.001727</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.903254</v>
+        <v>-1.905404</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.055162</v>
+        <v>-1.060901</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.940091</v>
+        <v>-2.947789</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.247228</v>
+        <v>-3.25854</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-3.436763</v>
+        <v>-3.447809</v>
       </c>
     </row>
     <row r="28">
@@ -2162,19 +2162,19 @@
         <v>-1.466632</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-4.504244</v>
+        <v>-4.547635</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.360734</v>
+        <v>-2.362586</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.410769</v>
+        <v>-1.418263</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.655545</v>
+        <v>-0.656232</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-20.586615</v>
+        <v>-20.586729</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.543435</v>
@@ -2189,19 +2189,19 @@
         <v>0.025161</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.87812</v>
+        <v>-1.88027</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.027571</v>
+        <v>-1.03331</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.910602</v>
+        <v>-2.9183</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.213875</v>
+        <v>-3.225187</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-3.41435</v>
+        <v>-3.425396</v>
       </c>
     </row>
     <row r="30">
@@ -2463,7 +2463,7 @@
         <v>0.030309</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.003364</v>
+        <v>0.030309</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>11.92256</v>
@@ -2481,34 +2481,34 @@
         <v>0.000824</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.010667</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005174</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003086</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.003588</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.047175</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.6504799999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.25555</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.627109</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.031393</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>1.869793</v>
       </c>
     </row>
     <row r="35">
@@ -2579,7 +2579,7 @@
         <v>0.030309</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.003364</v>
+        <v>0.030309</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>11.92256</v>
@@ -2597,34 +2597,34 @@
         <v>0.000824</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.010667</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005174</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003086</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.003588</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.047175</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.6504799999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.25555</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.627109</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.031393</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>1.869793</v>
       </c>
     </row>
     <row r="37">
@@ -3275,52 +3275,52 @@
         <v>0.050944</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.0476</v>
+        <v>0.020655</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.159049</v>
+        <v>0.12051</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.389008</v>
+        <v>1.354782</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.045761</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.08683399999999999</v>
+        <v>0.07799</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.019184</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.018813</v>
+        <v>0.008146</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.005474</v>
+        <v>0.0003</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.005132</v>
+        <v>0.002046</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.01291</v>
+        <v>0.009322</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.182184</v>
+        <v>0.135009</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.672504</v>
+        <v>0.022024</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.34973</v>
+        <v>0.09418</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.84956</v>
+        <v>0.222451</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.143579</v>
+        <v>0.112186</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.129223</v>
+        <v>0.25943</v>
       </c>
     </row>
     <row r="49">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -34852,7 +34852,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -39930,7 +39930,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -44696,7 +44696,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -47914,7 +47914,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
